--- a/XlsxSharp.Tests/Resource/Examples/Misc/Hyperlinks.xlsx
+++ b/XlsxSharp.Tests/Resource/Examples/Misc/Hyperlinks.xlsx
@@ -1,55 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Hyperlinks" sheetId="1" r:id="rId2"/>
-    <x:sheet name="Second Sheet" sheetId="2" r:id="rId3"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Hyperlinks" sheetId="1"/>
+    <sheet r:id="rId2" name="Second Sheet" sheetId="2"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="125725"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>Link to a web page, no tooltip - Yahoo!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Link to a web page, with a tooltip - Yahoo!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Link to a file - same folder</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Link to a file - Absolute</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Link to a file - relative address</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Link to an address in this worksheet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Link to an address in another worksheet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Link to a range in this worksheet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Link to an email message</x:t>
-  </x:si>
-  <x:si>
-    <x:t>This is no longer a link</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Odd looking link</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>Link to a web page, no tooltip - Yahoo!</t>
+  </si>
+  <si>
+    <t>Link to a web page, with a tooltip - Yahoo!</t>
+  </si>
+  <si>
+    <t>Link to a file - same folder</t>
+  </si>
+  <si>
+    <t>Link to a file - Absolute</t>
+  </si>
+  <si>
+    <t>Link to a file - relative address</t>
+  </si>
+  <si>
+    <t>Link to an address in this worksheet</t>
+  </si>
+  <si>
+    <t>Link to an address in another worksheet</t>
+  </si>
+  <si>
+    <t>Link to a range in this worksheet</t>
+  </si>
+  <si>
+    <t>Link to an email message</t>
+  </si>
+  <si>
+    <t>This is no longer a link</t>
+  </si>
+  <si>
+    <t>Odd looking link</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,119 +402,119 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:A14"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="38.567768" style="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:1">
-      <x:c r="A2" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:1">
-      <x:c r="A3" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:1">
-      <x:c r="A4" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:1">
-      <x:c r="A5" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:1">
-      <x:c r="A6" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:1">
-      <x:c r="A7" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:1">
-      <x:c r="A8" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:1">
-      <x:c r="A9" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:1">
-      <x:c r="A10" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:1">
-      <x:c r="A11" s="3" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:1">
-      <x:c r="A12" s="0">
-        <x:f>HYPERLINK("mailto:test@test.com", "Send Email through formula")</x:f>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:1">
-      <x:c r="A13" s="0">
-        <x:f>HYPERLINK("[Hyperlinks.xlsx]Hyperlinks!B2:C4", "Link to range through formula")</x:f>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:1">
-      <x:c r="A14" s="0">
-        <x:f>HYPERLINK("[../Test.xlsx]Sheet1!B2:C4", "Link to another file through formula")</x:f>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:hyperlinks>
-    <x:hyperlink ref="A1" r:id="rId13"/>
-    <x:hyperlink ref="A2" r:id="rId14" tooltip="Click to go to Yahoo!"/>
-    <x:hyperlink ref="A3" location="Hyperlinks!Test.xlsx" display="Link to a file - same folder"/>
-    <x:hyperlink ref="A4" r:id="rId15"/>
-    <x:hyperlink ref="A5" r:id="rId16"/>
-    <x:hyperlink ref="A6" location="Hyperlinks!B1" display="Link to an address in this worksheet"/>
-    <x:hyperlink ref="A7" location="'Second Sheet'!A1" display="Link to an address in another worksheet"/>
-    <x:hyperlink ref="A8" location="Hyperlinks!B1:C2" tooltip="SquareBox" display="Link to a range in this worksheet"/>
-    <x:hyperlink ref="A9" r:id="rId17"/>
-    <x:hyperlink ref="A11" location="Hyperlinks!B1:C2" display="Odd looking link"/>
-  </x:hyperlinks>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:A14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" style="0" customWidth="1" width="38.567768"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="0">
+        <f>HYPERLINK("mailto:test@test.com", "Send Email through formula")</f>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="0">
+        <f>HYPERLINK("[Hyperlinks.xlsx]Hyperlinks!B2:C4", "Link to range through formula")</f>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="0">
+        <f>HYPERLINK("[../Test.xlsx]Sheet1!B2:C4", "Link to another file through formula")</f>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId12"/>
+    <hyperlink ref="A2" r:id="rId13" tooltip="Click to go to Yahoo!"/>
+    <hyperlink ref="A3" location="Hyperlinks!Test.xlsx" display="Link to a file - same folder"/>
+    <hyperlink ref="A4" r:id="rId14"/>
+    <hyperlink ref="A5" r:id="rId15"/>
+    <hyperlink ref="A6" location="Hyperlinks!B1" display="Link to an address in this worksheet"/>
+    <hyperlink ref="A7" location="'Second Sheet'!A1" display="Link to an address in another worksheet"/>
+    <hyperlink ref="A8" location="Hyperlinks!B1:C2" display="Link to a range in this worksheet" tooltip="SquareBox"/>
+    <hyperlink ref="A9" r:id="rId16"/>
+    <hyperlink ref="A11" location="Hyperlinks!B1:C2" display="Odd looking link"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>